--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/53.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/53.xlsx
@@ -426,13 +426,13 @@
         <v>-6.89024345497777</v>
       </c>
       <c r="E2">
-        <v>-16.90319699601634</v>
+        <v>-16.47658757364974</v>
       </c>
       <c r="F2">
-        <v>4.744609176173317</v>
+        <v>1.681553374106779</v>
       </c>
       <c r="G2">
-        <v>-18.18258629269634</v>
+        <v>-17.41983188837704</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.438125737262834</v>
       </c>
       <c r="E3">
-        <v>-16.02092346204994</v>
+        <v>-16.62969980832309</v>
       </c>
       <c r="F3">
-        <v>5.192873569259047</v>
+        <v>2.393248541691586</v>
       </c>
       <c r="G3">
-        <v>-17.21232251512542</v>
+        <v>-17.84247947500599</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.92208485776221</v>
       </c>
       <c r="E4">
-        <v>-16.63594457397966</v>
+        <v>-18.36905950382523</v>
       </c>
       <c r="F4">
-        <v>4.868837778836353</v>
+        <v>2.421714559121388</v>
       </c>
       <c r="G4">
-        <v>-16.95536513297296</v>
+        <v>-16.82677241944754</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.39094372803216</v>
       </c>
       <c r="E5">
-        <v>-16.51651965744938</v>
+        <v>-20.32299188323281</v>
       </c>
       <c r="F5">
-        <v>4.81593326628916</v>
+        <v>2.896824682997045</v>
       </c>
       <c r="G5">
-        <v>-16.49817776759851</v>
+        <v>-16.7737331135499</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.854038996530035</v>
       </c>
       <c r="E6">
-        <v>-16.92998744824571</v>
+        <v>-18.92349416200633</v>
       </c>
       <c r="F6">
-        <v>4.687529691916014</v>
+        <v>2.415293055014887</v>
       </c>
       <c r="G6">
-        <v>-15.93335485079882</v>
+        <v>-16.79297419677448</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.336965959799025</v>
       </c>
       <c r="E7">
-        <v>-17.42083780288512</v>
+        <v>-20.30016384576014</v>
       </c>
       <c r="F7">
-        <v>5.104642500452066</v>
+        <v>2.183456213258583</v>
       </c>
       <c r="G7">
-        <v>-16.23369982563181</v>
+        <v>-17.53300942301619</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.856729544694185</v>
       </c>
       <c r="E8">
-        <v>-17.14201512975885</v>
+        <v>-20.14735954731932</v>
       </c>
       <c r="F8">
-        <v>4.398624963046047</v>
+        <v>2.894482059981927</v>
       </c>
       <c r="G8">
-        <v>-15.46790701014847</v>
+        <v>-15.7887021983507</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.430148192733125</v>
       </c>
       <c r="E9">
-        <v>-16.75760202819573</v>
+        <v>-20.46029521514537</v>
       </c>
       <c r="F9">
-        <v>5.226021519249472</v>
+        <v>2.616793425745866</v>
       </c>
       <c r="G9">
-        <v>-14.20852331669941</v>
+        <v>-15.58572911390501</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.066030034034199</v>
       </c>
       <c r="E10">
-        <v>-18.26120483838454</v>
+        <v>-22.03952354126228</v>
       </c>
       <c r="F10">
-        <v>5.108648485212004</v>
+        <v>3.236445377736008</v>
       </c>
       <c r="G10">
-        <v>-14.1750204039667</v>
+        <v>-14.11469022376397</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.771243572171265</v>
       </c>
       <c r="E11">
-        <v>-20.00419637004083</v>
+        <v>-21.72374399175941</v>
       </c>
       <c r="F11">
-        <v>5.377970608679791</v>
+        <v>2.052454878710258</v>
       </c>
       <c r="G11">
-        <v>-13.99230558142902</v>
+        <v>-15.79107616214896</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.545774037482342</v>
       </c>
       <c r="E12">
-        <v>-21.58543986709115</v>
+        <v>-22.1145150708293</v>
       </c>
       <c r="F12">
-        <v>5.000168803610992</v>
+        <v>2.923587577046691</v>
       </c>
       <c r="G12">
-        <v>-12.22465246536809</v>
+        <v>-14.40203828</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.387613691284803</v>
       </c>
       <c r="E13">
-        <v>-22.04120360511913</v>
+        <v>-22.56702736451977</v>
       </c>
       <c r="F13">
-        <v>5.075475684199495</v>
+        <v>2.447254782884503</v>
       </c>
       <c r="G13">
-        <v>-11.77752696590567</v>
+        <v>-12.15461479118174</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.29695871725708</v>
       </c>
       <c r="E14">
-        <v>-20.75418412129516</v>
+        <v>-22.32497137186177</v>
       </c>
       <c r="F14">
-        <v>4.903372415859065</v>
+        <v>3.338818334843582</v>
       </c>
       <c r="G14">
-        <v>-11.13087038341343</v>
+        <v>-12.89984583176282</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.268143460843675</v>
       </c>
       <c r="E15">
-        <v>-21.96127151040974</v>
+        <v>-25.30505143293345</v>
       </c>
       <c r="F15">
-        <v>5.041491083132243</v>
+        <v>3.348415799572417</v>
       </c>
       <c r="G15">
-        <v>-10.82101478789039</v>
+        <v>-12.10882206309813</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.293211556728987</v>
       </c>
       <c r="E16">
-        <v>-23.61028362098484</v>
+        <v>-26.5280065949709</v>
       </c>
       <c r="F16">
-        <v>5.371337042518173</v>
+        <v>3.28149034036544</v>
       </c>
       <c r="G16">
-        <v>-9.687300239557285</v>
+        <v>-10.91878534669716</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.362203536843893</v>
       </c>
       <c r="E17">
-        <v>-24.54289567202051</v>
+        <v>-27.90278337658951</v>
       </c>
       <c r="F17">
-        <v>5.254929884872369</v>
+        <v>3.243630636587891</v>
       </c>
       <c r="G17">
-        <v>-9.550243615019278</v>
+        <v>-12.03623487976009</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.463057394315599</v>
       </c>
       <c r="E18">
-        <v>-24.1989309002939</v>
+        <v>-27.69976735835164</v>
       </c>
       <c r="F18">
-        <v>5.5735912275857</v>
+        <v>2.463384752951814</v>
       </c>
       <c r="G18">
-        <v>-9.107862761931823</v>
+        <v>-9.58297051885318</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.584848518206011</v>
       </c>
       <c r="E19">
-        <v>-25.18790886730304</v>
+        <v>-28.72048087120653</v>
       </c>
       <c r="F19">
-        <v>5.442649535490377</v>
+        <v>2.861988520239714</v>
       </c>
       <c r="G19">
-        <v>-7.741604760459317</v>
+        <v>-9.842068898073173</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.720123681477581</v>
       </c>
       <c r="E20">
-        <v>-26.66747000898512</v>
+        <v>-28.56198880941207</v>
       </c>
       <c r="F20">
-        <v>5.477765686429853</v>
+        <v>3.537977739294251</v>
       </c>
       <c r="G20">
-        <v>-7.935160739029401</v>
+        <v>-9.555828254113454</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.862109105906618</v>
       </c>
       <c r="E21">
-        <v>-26.72920216665769</v>
+        <v>-29.84799844353232</v>
       </c>
       <c r="F21">
-        <v>5.069738411567706</v>
+        <v>3.302638560158911</v>
       </c>
       <c r="G21">
-        <v>-6.454151857179993</v>
+        <v>-8.373289128975816</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.005406265050021</v>
       </c>
       <c r="E22">
-        <v>-27.75939830408464</v>
+        <v>-28.93121793762748</v>
       </c>
       <c r="F22">
-        <v>5.677885997067769</v>
+        <v>3.278698742218006</v>
       </c>
       <c r="G22">
-        <v>-5.306364149578434</v>
+        <v>-8.056805465902695</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.146227548912986</v>
       </c>
       <c r="E23">
-        <v>-27.48984541725207</v>
+        <v>-32.00077385237971</v>
       </c>
       <c r="F23">
-        <v>4.937438196931791</v>
+        <v>4.102859695346095</v>
       </c>
       <c r="G23">
-        <v>-5.57537509912951</v>
+        <v>-8.906113573127806</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.280930293782411</v>
       </c>
       <c r="E24">
-        <v>-28.79020578550263</v>
+        <v>-29.89809015876817</v>
       </c>
       <c r="F24">
-        <v>4.836561271353673</v>
+        <v>3.071560502943572</v>
       </c>
       <c r="G24">
-        <v>-4.560988735248736</v>
+        <v>-7.424865162104559</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.406500038450023</v>
       </c>
       <c r="E25">
-        <v>-29.31048669271788</v>
+        <v>-30.95015656141517</v>
       </c>
       <c r="F25">
-        <v>4.96595060293615</v>
+        <v>2.706692826502085</v>
       </c>
       <c r="G25">
-        <v>-4.955467034789858</v>
+        <v>-7.740574456889651</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.5222998817855</v>
       </c>
       <c r="E26">
-        <v>-28.97784310601045</v>
+        <v>-32.10990328325355</v>
       </c>
       <c r="F26">
-        <v>5.577622063367722</v>
+        <v>2.885063522612097</v>
       </c>
       <c r="G26">
-        <v>-4.791812828290992</v>
+        <v>-7.424048137936257</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.62747182102156</v>
       </c>
       <c r="E27">
-        <v>-29.35748319596949</v>
+        <v>-31.49591013492357</v>
       </c>
       <c r="F27">
-        <v>4.920981850107776</v>
+        <v>3.56812368581693</v>
       </c>
       <c r="G27">
-        <v>-2.931064894145489</v>
+        <v>-5.062776104669937</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.720136740370087</v>
       </c>
       <c r="E28">
-        <v>-30.52857148096008</v>
+        <v>-30.25137905847657</v>
       </c>
       <c r="F28">
-        <v>5.334592321264792</v>
+        <v>4.110606587297077</v>
       </c>
       <c r="G28">
-        <v>-2.888786354352044</v>
+        <v>-5.911260625283628</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.798205432742721</v>
       </c>
       <c r="E29">
-        <v>-29.63769611061611</v>
+        <v>-31.78824124601472</v>
       </c>
       <c r="F29">
-        <v>4.682620786687024</v>
+        <v>3.029847234008201</v>
       </c>
       <c r="G29">
-        <v>-3.660572321013714</v>
+        <v>-5.571070136443518</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.859245676778283</v>
       </c>
       <c r="E30">
-        <v>-27.93085991543706</v>
+        <v>-30.12842872493132</v>
       </c>
       <c r="F30">
-        <v>4.801105489779049</v>
+        <v>3.09861663905381</v>
       </c>
       <c r="G30">
-        <v>-2.908280091636705</v>
+        <v>-4.613619529062229</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.899838041385179</v>
       </c>
       <c r="E31">
-        <v>-28.74064163748868</v>
+        <v>-30.68235619402357</v>
       </c>
       <c r="F31">
-        <v>4.970614311413912</v>
+        <v>2.709487738119131</v>
       </c>
       <c r="G31">
-        <v>-3.333047347393061</v>
+        <v>-5.743980668961576</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.918787427089018</v>
       </c>
       <c r="E32">
-        <v>-27.94691335579425</v>
+        <v>-30.2990978533324</v>
       </c>
       <c r="F32">
-        <v>4.562217584690116</v>
+        <v>2.575172933959608</v>
       </c>
       <c r="G32">
-        <v>-4.619131981282096</v>
+        <v>-5.070893846808004</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.916596364615258</v>
       </c>
       <c r="E33">
-        <v>-28.822303609269</v>
+        <v>-31.24446435141067</v>
       </c>
       <c r="F33">
-        <v>4.848138534175199</v>
+        <v>2.560986313819263</v>
       </c>
       <c r="G33">
-        <v>-3.66142215739761</v>
+        <v>-5.200643190933126</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.892728346432477</v>
       </c>
       <c r="E34">
-        <v>-27.27787207742703</v>
+        <v>-30.05157825678415</v>
       </c>
       <c r="F34">
-        <v>5.085740813054987</v>
+        <v>2.412653876469567</v>
       </c>
       <c r="G34">
-        <v>-3.600686746332288</v>
+        <v>-5.00243115897019</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.846540657557949</v>
       </c>
       <c r="E35">
-        <v>-27.63991904586626</v>
+        <v>-29.32920740426559</v>
       </c>
       <c r="F35">
-        <v>4.696625165998753</v>
+        <v>2.392574250625707</v>
       </c>
       <c r="G35">
-        <v>-3.411137139286286</v>
+        <v>-5.609398085479392</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.777638886956538</v>
       </c>
       <c r="E36">
-        <v>-26.80869047091432</v>
+        <v>-31.14508472507534</v>
       </c>
       <c r="F36">
-        <v>5.015940918960295</v>
+        <v>2.835127878836537</v>
       </c>
       <c r="G36">
-        <v>-3.943092059725023</v>
+        <v>-6.271709376031748</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.685154538925</v>
       </c>
       <c r="E37">
-        <v>-27.04342844957593</v>
+        <v>-27.92553895847805</v>
       </c>
       <c r="F37">
-        <v>4.853642207199399</v>
+        <v>1.98705030205482</v>
       </c>
       <c r="G37">
-        <v>-6.462948812180865</v>
+        <v>-7.356130132877311</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.569968581396516</v>
       </c>
       <c r="E38">
-        <v>-25.75947927112917</v>
+        <v>-28.24827877253071</v>
       </c>
       <c r="F38">
-        <v>5.595382260483744</v>
+        <v>2.820871675834358</v>
       </c>
       <c r="G38">
-        <v>-5.372703887067288</v>
+        <v>-7.185119427642171</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.436898240211757</v>
       </c>
       <c r="E39">
-        <v>-27.98627485186892</v>
+        <v>-27.03076683625048</v>
       </c>
       <c r="F39">
-        <v>5.602507876882625</v>
+        <v>3.349290555549774</v>
       </c>
       <c r="G39">
-        <v>-6.098762750076537</v>
+        <v>-8.359993619216946</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.291693411644913</v>
       </c>
       <c r="E40">
-        <v>-26.16469618228352</v>
+        <v>-28.45257182043874</v>
       </c>
       <c r="F40">
-        <v>5.47477030990133</v>
+        <v>3.587298734456933</v>
       </c>
       <c r="G40">
-        <v>-6.423748058210179</v>
+        <v>-8.765135888826263</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.141639418239067</v>
       </c>
       <c r="E41">
-        <v>-25.24237735266729</v>
+        <v>-25.70773692711752</v>
       </c>
       <c r="F41">
-        <v>5.597406790416185</v>
+        <v>3.292095099856079</v>
       </c>
       <c r="G41">
-        <v>-6.86467204892524</v>
+        <v>-7.480281713022021</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.995402431391649</v>
       </c>
       <c r="E42">
-        <v>-24.46837963222429</v>
+        <v>-25.69522928190834</v>
       </c>
       <c r="F42">
-        <v>5.62037576176101</v>
+        <v>3.645146943664034</v>
       </c>
       <c r="G42">
-        <v>-5.769935131496784</v>
+        <v>-8.241196992657251</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.861791693679982</v>
       </c>
       <c r="E43">
-        <v>-23.67955115940617</v>
+        <v>-22.5761929959113</v>
       </c>
       <c r="F43">
-        <v>5.791344166759606</v>
+        <v>3.592906781773886</v>
       </c>
       <c r="G43">
-        <v>-6.255431235875343</v>
+        <v>-8.799509965883006</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.749420339497398</v>
       </c>
       <c r="E44">
-        <v>-24.48171598817688</v>
+        <v>-24.14121097059213</v>
       </c>
       <c r="F44">
-        <v>6.254522486565338</v>
+        <v>2.842111016042137</v>
       </c>
       <c r="G44">
-        <v>-6.683696273814068</v>
+        <v>-7.227158438261777</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.668380138688833</v>
       </c>
       <c r="E45">
-        <v>-23.0962067231601</v>
+        <v>-24.22270086036016</v>
       </c>
       <c r="F45">
-        <v>5.96387155921027</v>
+        <v>4.059580812019433</v>
       </c>
       <c r="G45">
-        <v>-7.880603868160514</v>
+        <v>-9.386530346532345</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.627400556754883</v>
       </c>
       <c r="E46">
-        <v>-21.39150796771267</v>
+        <v>-21.70346548515306</v>
       </c>
       <c r="F46">
-        <v>6.319169935414617</v>
+        <v>3.052743309021579</v>
       </c>
       <c r="G46">
-        <v>-7.234432906459066</v>
+        <v>-9.759828360907251</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.631468153731243</v>
       </c>
       <c r="E47">
-        <v>-21.33377445258888</v>
+        <v>-23.02377830988142</v>
       </c>
       <c r="F47">
-        <v>6.492780832428143</v>
+        <v>3.531899179292508</v>
       </c>
       <c r="G47">
-        <v>-8.22205434607945</v>
+        <v>-9.419103032952952</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.682635536576356</v>
       </c>
       <c r="E48">
-        <v>-21.45527341021467</v>
+        <v>-23.40281158432343</v>
       </c>
       <c r="F48">
-        <v>6.494536971322078</v>
+        <v>4.419668808546766</v>
       </c>
       <c r="G48">
-        <v>-7.805191553059796</v>
+        <v>-10.34606124838232</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.779148764671536</v>
       </c>
       <c r="E49">
-        <v>-20.07163440496306</v>
+        <v>-20.26071178020532</v>
       </c>
       <c r="F49">
-        <v>6.519508935046872</v>
+        <v>4.509303131734089</v>
       </c>
       <c r="G49">
-        <v>-9.666516982199761</v>
+        <v>-10.42153262547111</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.914525840760441</v>
       </c>
       <c r="E50">
-        <v>-20.17410018633462</v>
+        <v>-19.66093351178541</v>
       </c>
       <c r="F50">
-        <v>6.763335566591295</v>
+        <v>4.892242471435051</v>
       </c>
       <c r="G50">
-        <v>-8.289716415856759</v>
+        <v>-10.10485537032598</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.082896755063606</v>
       </c>
       <c r="E51">
-        <v>-19.26738194967481</v>
+        <v>-20.51076958643487</v>
       </c>
       <c r="F51">
-        <v>6.446965488114108</v>
+        <v>4.738156194105509</v>
       </c>
       <c r="G51">
-        <v>-7.38580221943937</v>
+        <v>-9.718137159772946</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.277845597505272</v>
       </c>
       <c r="E52">
-        <v>-18.12192709180463</v>
+        <v>-19.99075585918607</v>
       </c>
       <c r="F52">
-        <v>6.862617056551621</v>
+        <v>4.455860180375076</v>
       </c>
       <c r="G52">
-        <v>-8.816723254183854</v>
+        <v>-12.49770916110196</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.490609093678994</v>
       </c>
       <c r="E53">
-        <v>-18.66864523027667</v>
+        <v>-18.20772808882796</v>
       </c>
       <c r="F53">
-        <v>6.686762940611315</v>
+        <v>4.916942730651726</v>
       </c>
       <c r="G53">
-        <v>-9.285744345112441</v>
+        <v>-12.19812707028153</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.712036319773787</v>
       </c>
       <c r="E54">
-        <v>-16.41311195348423</v>
+        <v>-17.03476727983519</v>
       </c>
       <c r="F54">
-        <v>6.466910918438715</v>
+        <v>3.788888568867415</v>
       </c>
       <c r="G54">
-        <v>-9.019532277551571</v>
+        <v>-12.2225557647916</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.933046267958902</v>
       </c>
       <c r="E55">
-        <v>-16.07278807485979</v>
+        <v>-16.83526082895327</v>
       </c>
       <c r="F55">
-        <v>7.445275777067543</v>
+        <v>4.473824155872187</v>
       </c>
       <c r="G55">
-        <v>-8.413077221605644</v>
+        <v>-11.96669595125078</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.143159138722073</v>
       </c>
       <c r="E56">
-        <v>-15.34132178229683</v>
+        <v>-16.14159370893233</v>
       </c>
       <c r="F56">
-        <v>6.67029168317405</v>
+        <v>4.682146960532623</v>
       </c>
       <c r="G56">
-        <v>-10.69568853042739</v>
+        <v>-14.37210041449163</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.335848172088056</v>
       </c>
       <c r="E57">
-        <v>-16.77084781466817</v>
+        <v>-15.90057473682209</v>
       </c>
       <c r="F57">
-        <v>7.072947823796444</v>
+        <v>4.218647234174605</v>
       </c>
       <c r="G57">
-        <v>-9.050050919275966</v>
+        <v>-12.2777590363077</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.507482591401528</v>
       </c>
       <c r="E58">
-        <v>-15.17537585228574</v>
+        <v>-14.11599369987936</v>
       </c>
       <c r="F58">
-        <v>7.022077781590527</v>
+        <v>4.608906028246702</v>
       </c>
       <c r="G58">
-        <v>-9.850724760546989</v>
+        <v>-12.22894102194628</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.655351912682048</v>
       </c>
       <c r="E59">
-        <v>-13.91450830585608</v>
+        <v>-15.04475201953449</v>
       </c>
       <c r="F59">
-        <v>6.906744188098751</v>
+        <v>4.499921042529982</v>
       </c>
       <c r="G59">
-        <v>-10.16850450613609</v>
+        <v>-12.81574156075114</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.778277838244795</v>
       </c>
       <c r="E60">
-        <v>-14.32650887107393</v>
+        <v>-14.8713024080927</v>
       </c>
       <c r="F60">
-        <v>6.867711516078838</v>
+        <v>5.236868162021729</v>
       </c>
       <c r="G60">
-        <v>-9.33544500807335</v>
+        <v>-13.23400543537667</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.876929810895644</v>
       </c>
       <c r="E61">
-        <v>-13.55095335557229</v>
+        <v>-13.29309298862752</v>
       </c>
       <c r="F61">
-        <v>7.334471696534276</v>
+        <v>4.112967434395054</v>
       </c>
       <c r="G61">
-        <v>-10.01685957054479</v>
+        <v>-13.7760665182185</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.951965567225905</v>
       </c>
       <c r="E62">
-        <v>-13.8387741065518</v>
+        <v>-12.91182264802572</v>
       </c>
       <c r="F62">
-        <v>6.845020876181355</v>
+        <v>4.847026865120642</v>
       </c>
       <c r="G62">
-        <v>-9.579252894826329</v>
+        <v>-13.253591046865</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.005869588006854</v>
       </c>
       <c r="E63">
-        <v>-12.61258561407287</v>
+        <v>-15.04407274843334</v>
       </c>
       <c r="F63">
-        <v>6.592445028128563</v>
+        <v>4.493540956793621</v>
       </c>
       <c r="G63">
-        <v>-9.86395136465311</v>
+        <v>-13.1940106257886</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.044867117887224</v>
       </c>
       <c r="E64">
-        <v>-13.72732383274903</v>
+        <v>-14.09054367595625</v>
       </c>
       <c r="F64">
-        <v>6.515401889463792</v>
+        <v>4.001687870972581</v>
       </c>
       <c r="G64">
-        <v>-10.40282966258228</v>
+        <v>-14.8158478963586</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.075406042409094</v>
       </c>
       <c r="E65">
-        <v>-12.9570938026804</v>
+        <v>-12.52846015243238</v>
       </c>
       <c r="F65">
-        <v>6.408923543507943</v>
+        <v>4.414468317991991</v>
       </c>
       <c r="G65">
-        <v>-9.810795575390106</v>
+        <v>-14.99079770807585</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.103042234244786</v>
       </c>
       <c r="E66">
-        <v>-14.1232845430317</v>
+        <v>-14.60760483815205</v>
       </c>
       <c r="F66">
-        <v>6.377077787074719</v>
+        <v>4.560739777243522</v>
       </c>
       <c r="G66">
-        <v>-9.961469269399807</v>
+        <v>-12.5894061788022</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.132588890583569</v>
       </c>
       <c r="E67">
-        <v>-12.88054900652875</v>
+        <v>-12.47592079699539</v>
       </c>
       <c r="F67">
-        <v>6.330576554551167</v>
+        <v>4.393646474955222</v>
       </c>
       <c r="G67">
-        <v>-9.414532291320645</v>
+        <v>-14.00482180106753</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.167090402164195</v>
       </c>
       <c r="E68">
-        <v>-14.2994512388781</v>
+        <v>-13.80241951721822</v>
       </c>
       <c r="F68">
-        <v>6.072888022888296</v>
+        <v>4.657128608233273</v>
       </c>
       <c r="G68">
-        <v>-9.580739288192758</v>
+        <v>-13.68862852610242</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.206760117502134</v>
       </c>
       <c r="E69">
-        <v>-13.63191794235543</v>
+        <v>-13.01629907185669</v>
       </c>
       <c r="F69">
-        <v>6.259051999523846</v>
+        <v>3.148346847713475</v>
       </c>
       <c r="G69">
-        <v>-8.795680780323135</v>
+        <v>-11.29849814922078</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.254426872728499</v>
       </c>
       <c r="E70">
-        <v>-12.88245549408598</v>
+        <v>-13.81563813284661</v>
       </c>
       <c r="F70">
-        <v>5.728645038041711</v>
+        <v>3.763833768402342</v>
       </c>
       <c r="G70">
-        <v>-8.320448336982519</v>
+        <v>-11.48462216095872</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.31350196455789</v>
       </c>
       <c r="E71">
-        <v>-12.24495050870817</v>
+        <v>-12.80945196460833</v>
       </c>
       <c r="F71">
-        <v>6.085711150283633</v>
+        <v>3.872030148351596</v>
       </c>
       <c r="G71">
-        <v>-9.010105328011287</v>
+        <v>-13.01658513240475</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.384524492503925</v>
       </c>
       <c r="E72">
-        <v>-13.9403794778619</v>
+        <v>-14.57013171573858</v>
       </c>
       <c r="F72">
-        <v>5.618374426115847</v>
+        <v>3.763429525109776</v>
       </c>
       <c r="G72">
-        <v>-7.325923207201063</v>
+        <v>-11.27573959648447</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.467290626602338</v>
       </c>
       <c r="E73">
-        <v>-12.80792134039373</v>
+        <v>-15.76085319978943</v>
       </c>
       <c r="F73">
-        <v>4.801408672248473</v>
+        <v>3.373926202109031</v>
       </c>
       <c r="G73">
-        <v>-8.035966427778661</v>
+        <v>-11.19700012272248</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.56116907509875</v>
       </c>
       <c r="E74">
-        <v>-12.54497549713836</v>
+        <v>-14.00472003656288</v>
       </c>
       <c r="F74">
-        <v>4.9424117148182</v>
+        <v>2.682872293467183</v>
       </c>
       <c r="G74">
-        <v>-6.647025341665714</v>
+        <v>-10.92289015486802</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.661831629233936</v>
       </c>
       <c r="E75">
-        <v>-13.48678940735761</v>
+        <v>-11.15586609528547</v>
       </c>
       <c r="F75">
-        <v>5.232013929041324</v>
+        <v>4.434218253609536</v>
       </c>
       <c r="G75">
-        <v>-7.679655297417001</v>
+        <v>-9.21613322972882</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.769364949379766</v>
       </c>
       <c r="E76">
-        <v>-11.60907577397312</v>
+        <v>-14.07494308299982</v>
       </c>
       <c r="F76">
-        <v>5.175554063601315</v>
+        <v>3.596846497141601</v>
       </c>
       <c r="G76">
-        <v>-7.575099172425294</v>
+        <v>-10.15811615867889</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.886485731805931</v>
       </c>
       <c r="E77">
-        <v>-12.77195167135081</v>
+        <v>-15.35592611097156</v>
       </c>
       <c r="F77">
-        <v>5.25209521161999</v>
+        <v>3.370475223508968</v>
       </c>
       <c r="G77">
-        <v>-6.469307819563069</v>
+        <v>-8.189927905790926</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.0143464620981</v>
       </c>
       <c r="E78">
-        <v>-14.0445841932524</v>
+        <v>-13.7920719541107</v>
       </c>
       <c r="F78">
-        <v>4.600557741561288</v>
+        <v>3.123724455032663</v>
       </c>
       <c r="G78">
-        <v>-6.91549488965948</v>
+        <v>-7.759543198724801</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.154395016510038</v>
       </c>
       <c r="E79">
-        <v>-15.23232594140621</v>
+        <v>-15.04807139098212</v>
       </c>
       <c r="F79">
-        <v>4.308352796958569</v>
+        <v>2.795980892115038</v>
       </c>
       <c r="G79">
-        <v>-5.894201554396075</v>
+        <v>-9.739606192436392</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.308211123673004</v>
       </c>
       <c r="E80">
-        <v>-16.05932945010899</v>
+        <v>-16.54205119390463</v>
       </c>
       <c r="F80">
-        <v>4.163786117821999</v>
+        <v>2.992618746191585</v>
       </c>
       <c r="G80">
-        <v>-4.830347494285111</v>
+        <v>-8.918309873664262</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.47466873159546</v>
       </c>
       <c r="E81">
-        <v>-15.68718851310666</v>
+        <v>-15.06283421624712</v>
       </c>
       <c r="F81">
-        <v>4.763476072139478</v>
+        <v>2.801050500620171</v>
       </c>
       <c r="G81">
-        <v>-5.69485750099513</v>
+        <v>-7.537916369713667</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.653580618149372</v>
       </c>
       <c r="E82">
-        <v>-17.0861971591403</v>
+        <v>-18.1872639147873</v>
       </c>
       <c r="F82">
-        <v>4.318561596830669</v>
+        <v>2.362613858401255</v>
       </c>
       <c r="G82">
-        <v>-4.283935511655462</v>
+        <v>-7.448407926793575</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.848125685441426</v>
       </c>
       <c r="E83">
-        <v>-17.36569457489372</v>
+        <v>-16.91483970269006</v>
       </c>
       <c r="F83">
-        <v>4.076837361754552</v>
+        <v>2.174102288546171</v>
       </c>
       <c r="G83">
-        <v>-3.546323467535408</v>
+        <v>-7.020372574364012</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.059730820866283</v>
       </c>
       <c r="E84">
-        <v>-17.28880108624348</v>
+        <v>-16.20207147930477</v>
       </c>
       <c r="F84">
-        <v>4.148098495947782</v>
+        <v>2.478585294793185</v>
       </c>
       <c r="G84">
-        <v>-4.177394247620291</v>
+        <v>-8.310000927537246</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.287851969730505</v>
       </c>
       <c r="E85">
-        <v>-17.86319725785039</v>
+        <v>-19.32529660375891</v>
       </c>
       <c r="F85">
-        <v>4.069385368598967</v>
+        <v>1.668089090341676</v>
       </c>
       <c r="G85">
-        <v>-4.378677502962868</v>
+        <v>-5.406474219357093</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.531084312868586</v>
       </c>
       <c r="E86">
-        <v>-20.35236356564656</v>
+        <v>-19.21709777429364</v>
       </c>
       <c r="F86">
-        <v>3.757647520638235</v>
+        <v>2.021641268060922</v>
       </c>
       <c r="G86">
-        <v>-3.277552047158172</v>
+        <v>-6.902425784188211</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.785603501018275</v>
       </c>
       <c r="E87">
-        <v>-19.95137172074136</v>
+        <v>-20.74720574284935</v>
       </c>
       <c r="F87">
-        <v>4.252482729109353</v>
+        <v>1.933030806983459</v>
       </c>
       <c r="G87">
-        <v>-3.132994550135276</v>
+        <v>-5.79926925223822</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.04511733663702</v>
       </c>
       <c r="E88">
-        <v>-21.17148300110199</v>
+        <v>-23.5345131938885</v>
       </c>
       <c r="F88">
-        <v>3.38271683698754</v>
+        <v>1.961201925617865</v>
       </c>
       <c r="G88">
-        <v>-3.241839231705176</v>
+        <v>-5.711145484816213</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.309050610034138</v>
       </c>
       <c r="E89">
-        <v>-23.2596257646749</v>
+        <v>-22.58501899175224</v>
       </c>
       <c r="F89">
-        <v>3.63964492737464</v>
+        <v>1.37470455055737</v>
       </c>
       <c r="G89">
-        <v>-3.042304867453784</v>
+        <v>-5.879521369139119</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.577660553341932</v>
       </c>
       <c r="E90">
-        <v>-25.65867543971842</v>
+        <v>-25.81931399819251</v>
       </c>
       <c r="F90">
-        <v>3.137921015581841</v>
+        <v>0.7743717831353177</v>
       </c>
       <c r="G90">
-        <v>-2.944012594419058</v>
+        <v>-3.747242507284887</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.849667773081501</v>
       </c>
       <c r="E91">
-        <v>-26.24924279200673</v>
+        <v>-24.76830499422631</v>
       </c>
       <c r="F91">
-        <v>2.517730624779879</v>
+        <v>1.210684491333456</v>
       </c>
       <c r="G91">
-        <v>-2.883447806874827</v>
+        <v>-3.655345335069518</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.124624917610275</v>
       </c>
       <c r="E92">
-        <v>-28.90135265154689</v>
+        <v>-26.2715998681826</v>
       </c>
       <c r="F92">
-        <v>2.623176824951839</v>
+        <v>1.071729172983451</v>
       </c>
       <c r="G92">
-        <v>-1.997239081992201</v>
+        <v>-4.230812534608051</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.402969295645331</v>
       </c>
       <c r="E93">
-        <v>-27.85928285527183</v>
+        <v>-28.45950944261849</v>
       </c>
       <c r="F93">
-        <v>2.591195216264556</v>
+        <v>0.1106175506201298</v>
       </c>
       <c r="G93">
-        <v>-1.717701973678427</v>
+        <v>-5.697361073044986</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.679655889571182</v>
       </c>
       <c r="E94">
-        <v>-31.8284314528328</v>
+        <v>-30.91730021825251</v>
       </c>
       <c r="F94">
-        <v>2.592780711473514</v>
+        <v>0.8210055544433187</v>
       </c>
       <c r="G94">
-        <v>-2.935816102963565</v>
+        <v>-6.130541380879759</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.95785499560823</v>
       </c>
       <c r="E95">
-        <v>-31.66426747734373</v>
+        <v>-34.00943057593298</v>
       </c>
       <c r="F95">
-        <v>1.724348490870208</v>
+        <v>-0.9491725102342793</v>
       </c>
       <c r="G95">
-        <v>-2.752970031563508</v>
+        <v>-5.073564761157392</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-10.24323108220595</v>
       </c>
       <c r="E96">
-        <v>-35.42999475824315</v>
+        <v>-34.46575584473791</v>
       </c>
       <c r="F96">
-        <v>1.423122625251001</v>
+        <v>-0.3426394128022728</v>
       </c>
       <c r="G96">
-        <v>-1.123761496760221</v>
+        <v>-6.488000938787225</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.53513104713157</v>
       </c>
       <c r="E97">
-        <v>-36.99558784912296</v>
+        <v>-37.38094966599068</v>
       </c>
       <c r="F97">
-        <v>1.056545198490136</v>
+        <v>-0.8118242246457045</v>
       </c>
       <c r="G97">
-        <v>-1.942698617231111</v>
+        <v>-5.424599687251465</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.83421424574422</v>
       </c>
       <c r="E98">
-        <v>-38.9736456738064</v>
+        <v>-37.60449778537933</v>
       </c>
       <c r="F98">
-        <v>0.8776675415296105</v>
+        <v>-0.9553446757525383</v>
       </c>
       <c r="G98">
-        <v>-3.025147359919447</v>
+        <v>-6.989906432184568</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.1327203883703</v>
       </c>
       <c r="E99">
-        <v>-41.25949934831719</v>
+        <v>-39.60006721905044</v>
       </c>
       <c r="F99">
-        <v>0.05270307202080519</v>
+        <v>-0.5697984638349672</v>
       </c>
       <c r="G99">
-        <v>-2.46601080008227</v>
+        <v>-4.431032674165368</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.42477656600282</v>
       </c>
       <c r="E100">
-        <v>-43.76606405325083</v>
+        <v>-44.7043480179811</v>
       </c>
       <c r="F100">
-        <v>0.2142993282241271</v>
+        <v>-1.406029558389249</v>
       </c>
       <c r="G100">
-        <v>-2.447905019517254</v>
+        <v>-6.399529361879917</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.69080116631625</v>
       </c>
       <c r="E101">
-        <v>-46.27982903185666</v>
+        <v>-46.37187253029956</v>
       </c>
       <c r="F101">
-        <v>0.01830428725215292</v>
+        <v>-1.192390291737645</v>
       </c>
       <c r="G101">
-        <v>-3.685788508698046</v>
+        <v>-8.356902708507949</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.93798726746322</v>
       </c>
       <c r="E102">
-        <v>-47.7437737309233</v>
+        <v>-46.52594027298853</v>
       </c>
       <c r="F102">
-        <v>-0.08874149037461319</v>
+        <v>-2.398579380423616</v>
       </c>
       <c r="G102">
-        <v>-4.02447291684237</v>
+        <v>-7.591016378210161</v>
       </c>
     </row>
   </sheetData>
